--- a/selenium/Selenium_E2E_Test_Report_Traverse.xlsx
+++ b/selenium/Selenium_E2E_Test_Report_Traverse.xlsx
@@ -17,7 +17,7 @@
     <t>Traverse Web Selenium E2E Test Report</t>
   </si>
   <si>
-    <t>Automated &amp; Simulated Web E2E Validation Summary — Generated 17/6/2026, 3:02:17 pm</t>
+    <t>Automated &amp; Simulated Web E2E Validation Summary — Generated 18/6/2026, 9:28:40 am</t>
   </si>
   <si>
     <t>Metrics Dashboard</t>
@@ -134,7 +134,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-17</t>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>TC_WEB_UI_002</t>

--- a/selenium/Selenium_E2E_Test_Report_Traverse.xlsx
+++ b/selenium/Selenium_E2E_Test_Report_Traverse.xlsx
@@ -17,7 +17,7 @@
     <t>Traverse Web Selenium E2E Test Report</t>
   </si>
   <si>
-    <t>Automated &amp; Simulated Web E2E Validation Summary — Generated 18/6/2026, 9:28:40 am</t>
+    <t>Automated &amp; Simulated Web E2E Validation Summary — Generated 18/6/2026, 9:38:21 am</t>
   </si>
   <si>
     <t>Metrics Dashboard</t>
@@ -44,7 +44,7 @@
     <t>Selenium Driver</t>
   </si>
   <si>
-    <t>Headless Chrome Selenium Driver (Simulated Fallback)</t>
+    <t>Headless Chrome Selenium Driver (Active Web Session)</t>
   </si>
   <si>
     <t>Total Test Cases</t>

--- a/selenium/Selenium_E2E_Test_Report_Traverse.xlsx
+++ b/selenium/Selenium_E2E_Test_Report_Traverse.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="823">
   <si>
     <t>Traverse Web Selenium E2E Test Report</t>
   </si>
   <si>
-    <t>Automated &amp; Simulated Web E2E Validation Summary — Generated 18/6/2026, 9:38:21 am</t>
+    <t>Automated &amp; Simulated Web E2E Validation Summary — Generated 22/6/2026, 2:08:16 pm</t>
   </si>
   <si>
     <t>Metrics Dashboard</t>
@@ -44,7 +44,7 @@
     <t>Selenium Driver</t>
   </si>
   <si>
-    <t>Headless Chrome Selenium Driver (Active Web Session)</t>
+    <t>Headless Chrome Selenium Driver (Simulated Fallback)</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -134,7 +134,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-18</t>
+    <t>2026-06-22</t>
   </si>
   <si>
     <t>TC_WEB_UI_002</t>
@@ -479,6 +479,492 @@
     <t>Outfit font loaded and rendered successfully.</t>
   </si>
   <si>
+    <t>TC_WEB_UI_027</t>
+  </si>
+  <si>
+    <t>Verify Splash Screen behaves correctly under Accessibility Contrast conditions (expanded case 027).</t>
+  </si>
+  <si>
+    <t>Splash Screen should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Splash Screen execution under Accessibility Contrast conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_028</t>
+  </si>
+  <si>
+    <t>Verify Login Page behaves correctly under Performance Index conditions (expanded case 028).</t>
+  </si>
+  <si>
+    <t>Login Page should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Login Page execution under Performance Index conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_029</t>
+  </si>
+  <si>
+    <t>Verify Signup Page behaves correctly under DOM Elements conditions (expanded case 029).</t>
+  </si>
+  <si>
+    <t>Signup Page should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Signup Page execution under DOM Elements conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_030</t>
+  </si>
+  <si>
+    <t>Verify Navbar behaves correctly under Focus State conditions (expanded case 030).</t>
+  </si>
+  <si>
+    <t>Navbar should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Navbar execution under Focus State conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_031</t>
+  </si>
+  <si>
+    <t>Verify Home Dashboard behaves correctly under Click Interactions conditions (expanded case 031).</t>
+  </si>
+  <si>
+    <t>Home Dashboard should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Home Dashboard execution under Click Interactions conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_032</t>
+  </si>
+  <si>
+    <t>Verify Destinations behaves correctly under Keyboard Navigation conditions (expanded case 032).</t>
+  </si>
+  <si>
+    <t>Destinations should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Destinations execution under Keyboard Navigation conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_033</t>
+  </si>
+  <si>
+    <t>Verify Travel Wizard behaves correctly under Touch Target Limits conditions (expanded case 033).</t>
+  </si>
+  <si>
+    <t>Travel Wizard should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Travel Wizard execution under Touch Target Limits conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_034</t>
+  </si>
+  <si>
+    <t>Verify Itinerary Result behaves correctly under State Storage Sync conditions (expanded case 034).</t>
+  </si>
+  <si>
+    <t>Itinerary Result should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Itinerary Result execution under State Storage Sync conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_035</t>
+  </si>
+  <si>
+    <t>Verify Settings Page behaves correctly under Boundary Checks conditions (expanded case 035).</t>
+  </si>
+  <si>
+    <t>Settings Page should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Settings Page execution under Boundary Checks conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_036</t>
+  </si>
+  <si>
+    <t>Verify Profile Page behaves correctly under Error Recovery conditions (expanded case 036).</t>
+  </si>
+  <si>
+    <t>Profile Page should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Profile Page execution under Error Recovery conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_037</t>
+  </si>
+  <si>
+    <t>Verify Alerts &amp; Toasts behaves correctly under Mobile Views conditions (expanded case 037).</t>
+  </si>
+  <si>
+    <t>Alerts &amp; Toasts should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Alerts &amp; Toasts execution under Mobile Views conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_038</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Verify Forms behaves correctly under Desktop Sizing conditions (expanded case 038).</t>
+  </si>
+  <si>
+    <t>Forms should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Forms execution under Desktop Sizing conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_039</t>
+  </si>
+  <si>
+    <t>Buttons</t>
+  </si>
+  <si>
+    <t>Verify Buttons behaves correctly under Accessibility Contrast conditions (expanded case 039).</t>
+  </si>
+  <si>
+    <t>Buttons should operate within baseline specifications and visual guidelines.</t>
+  </si>
+  <si>
+    <t>Verified Buttons execution under Accessibility Contrast conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_040</t>
+  </si>
+  <si>
+    <t>Verify Splash Screen behaves correctly under Performance Index conditions (expanded case 040).</t>
+  </si>
+  <si>
+    <t>Verified Splash Screen execution under Performance Index conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_041</t>
+  </si>
+  <si>
+    <t>Verify Login Page behaves correctly under DOM Elements conditions (expanded case 041).</t>
+  </si>
+  <si>
+    <t>Verified Login Page execution under DOM Elements conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_042</t>
+  </si>
+  <si>
+    <t>Verify Signup Page behaves correctly under Focus State conditions (expanded case 042).</t>
+  </si>
+  <si>
+    <t>Verified Signup Page execution under Focus State conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_043</t>
+  </si>
+  <si>
+    <t>Verify Navbar behaves correctly under Click Interactions conditions (expanded case 043).</t>
+  </si>
+  <si>
+    <t>Verified Navbar execution under Click Interactions conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_044</t>
+  </si>
+  <si>
+    <t>Verify Home Dashboard behaves correctly under Keyboard Navigation conditions (expanded case 044).</t>
+  </si>
+  <si>
+    <t>Verified Home Dashboard execution under Keyboard Navigation conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_045</t>
+  </si>
+  <si>
+    <t>Verify Destinations behaves correctly under Touch Target Limits conditions (expanded case 045).</t>
+  </si>
+  <si>
+    <t>Verified Destinations execution under Touch Target Limits conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_046</t>
+  </si>
+  <si>
+    <t>Verify Travel Wizard behaves correctly under State Storage Sync conditions (expanded case 046).</t>
+  </si>
+  <si>
+    <t>Verified Travel Wizard execution under State Storage Sync conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_047</t>
+  </si>
+  <si>
+    <t>Verify Itinerary Result behaves correctly under Boundary Checks conditions (expanded case 047).</t>
+  </si>
+  <si>
+    <t>Verified Itinerary Result execution under Boundary Checks conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_048</t>
+  </si>
+  <si>
+    <t>Verify Settings Page behaves correctly under Error Recovery conditions (expanded case 048).</t>
+  </si>
+  <si>
+    <t>Verified Settings Page execution under Error Recovery conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_049</t>
+  </si>
+  <si>
+    <t>Verify Profile Page behaves correctly under Mobile Views conditions (expanded case 049).</t>
+  </si>
+  <si>
+    <t>Verified Profile Page execution under Mobile Views conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_050</t>
+  </si>
+  <si>
+    <t>Verify Alerts &amp; Toasts behaves correctly under Desktop Sizing conditions (expanded case 050).</t>
+  </si>
+  <si>
+    <t>Verified Alerts &amp; Toasts execution under Desktop Sizing conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_051</t>
+  </si>
+  <si>
+    <t>Verify Forms behaves correctly under Accessibility Contrast conditions (expanded case 051).</t>
+  </si>
+  <si>
+    <t>Verified Forms execution under Accessibility Contrast conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_052</t>
+  </si>
+  <si>
+    <t>Verify Buttons behaves correctly under Performance Index conditions (expanded case 052).</t>
+  </si>
+  <si>
+    <t>Verified Buttons execution under Performance Index conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_053</t>
+  </si>
+  <si>
+    <t>Verify Splash Screen behaves correctly under DOM Elements conditions (expanded case 053).</t>
+  </si>
+  <si>
+    <t>Verified Splash Screen execution under DOM Elements conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_054</t>
+  </si>
+  <si>
+    <t>Verify Login Page behaves correctly under Focus State conditions (expanded case 054).</t>
+  </si>
+  <si>
+    <t>Verified Login Page execution under Focus State conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_055</t>
+  </si>
+  <si>
+    <t>Verify Signup Page behaves correctly under Click Interactions conditions (expanded case 055).</t>
+  </si>
+  <si>
+    <t>Verified Signup Page execution under Click Interactions conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_056</t>
+  </si>
+  <si>
+    <t>Verify Navbar behaves correctly under Keyboard Navigation conditions (expanded case 056).</t>
+  </si>
+  <si>
+    <t>Verified Navbar execution under Keyboard Navigation conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_057</t>
+  </si>
+  <si>
+    <t>Verify Home Dashboard behaves correctly under Touch Target Limits conditions (expanded case 057).</t>
+  </si>
+  <si>
+    <t>Verified Home Dashboard execution under Touch Target Limits conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_058</t>
+  </si>
+  <si>
+    <t>Verify Destinations behaves correctly under State Storage Sync conditions (expanded case 058).</t>
+  </si>
+  <si>
+    <t>Verified Destinations execution under State Storage Sync conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_059</t>
+  </si>
+  <si>
+    <t>Verify Travel Wizard behaves correctly under Boundary Checks conditions (expanded case 059).</t>
+  </si>
+  <si>
+    <t>Verified Travel Wizard execution under Boundary Checks conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_060</t>
+  </si>
+  <si>
+    <t>Verify Itinerary Result behaves correctly under Error Recovery conditions (expanded case 060).</t>
+  </si>
+  <si>
+    <t>Verified Itinerary Result execution under Error Recovery conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_061</t>
+  </si>
+  <si>
+    <t>Verify Settings Page behaves correctly under Mobile Views conditions (expanded case 061).</t>
+  </si>
+  <si>
+    <t>Verified Settings Page execution under Mobile Views conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_062</t>
+  </si>
+  <si>
+    <t>Verify Profile Page behaves correctly under Desktop Sizing conditions (expanded case 062).</t>
+  </si>
+  <si>
+    <t>Verified Profile Page execution under Desktop Sizing conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_063</t>
+  </si>
+  <si>
+    <t>Verify Alerts &amp; Toasts behaves correctly under Accessibility Contrast conditions (expanded case 063).</t>
+  </si>
+  <si>
+    <t>Verified Alerts &amp; Toasts execution under Accessibility Contrast conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_064</t>
+  </si>
+  <si>
+    <t>Verify Forms behaves correctly under Performance Index conditions (expanded case 064).</t>
+  </si>
+  <si>
+    <t>Verified Forms execution under Performance Index conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_065</t>
+  </si>
+  <si>
+    <t>Verify Buttons behaves correctly under DOM Elements conditions (expanded case 065).</t>
+  </si>
+  <si>
+    <t>Verified Buttons execution under DOM Elements conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_066</t>
+  </si>
+  <si>
+    <t>Verify Splash Screen behaves correctly under Focus State conditions (expanded case 066).</t>
+  </si>
+  <si>
+    <t>Verified Splash Screen execution under Focus State conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_067</t>
+  </si>
+  <si>
+    <t>Verify Login Page behaves correctly under Click Interactions conditions (expanded case 067).</t>
+  </si>
+  <si>
+    <t>Verified Login Page execution under Click Interactions conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_068</t>
+  </si>
+  <si>
+    <t>Verify Signup Page behaves correctly under Keyboard Navigation conditions (expanded case 068).</t>
+  </si>
+  <si>
+    <t>Verified Signup Page execution under Keyboard Navigation conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_069</t>
+  </si>
+  <si>
+    <t>Verify Navbar behaves correctly under Touch Target Limits conditions (expanded case 069).</t>
+  </si>
+  <si>
+    <t>Verified Navbar execution under Touch Target Limits conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_070</t>
+  </si>
+  <si>
+    <t>Verify Home Dashboard behaves correctly under State Storage Sync conditions (expanded case 070).</t>
+  </si>
+  <si>
+    <t>Verified Home Dashboard execution under State Storage Sync conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_071</t>
+  </si>
+  <si>
+    <t>Verify Destinations behaves correctly under Boundary Checks conditions (expanded case 071).</t>
+  </si>
+  <si>
+    <t>Verified Destinations execution under Boundary Checks conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_072</t>
+  </si>
+  <si>
+    <t>Verify Travel Wizard behaves correctly under Error Recovery conditions (expanded case 072).</t>
+  </si>
+  <si>
+    <t>Verified Travel Wizard execution under Error Recovery conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_073</t>
+  </si>
+  <si>
+    <t>Verify Itinerary Result behaves correctly under Mobile Views conditions (expanded case 073).</t>
+  </si>
+  <si>
+    <t>Verified Itinerary Result execution under Mobile Views conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_074</t>
+  </si>
+  <si>
+    <t>Verify Settings Page behaves correctly under Desktop Sizing conditions (expanded case 074).</t>
+  </si>
+  <si>
+    <t>Verified Settings Page execution under Desktop Sizing conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_UI_075</t>
+  </si>
+  <si>
+    <t>Verify Profile Page behaves correctly under Accessibility Contrast conditions (expanded case 075).</t>
+  </si>
+  <si>
+    <t>Verified Profile Page execution under Accessibility Contrast conditions successfully.</t>
+  </si>
+  <si>
     <t>TC_WEB_FUNC_001</t>
   </si>
   <si>
@@ -923,6 +1409,123 @@
     <t>History popstates handled successfully.</t>
   </si>
   <si>
+    <t>TC_WEB_FUNC_037</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_038</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_039</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_040</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_041</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_042</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_043</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_044</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_045</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_046</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_047</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_048</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_049</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_050</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_051</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_052</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_053</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_054</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_055</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_056</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_057</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_058</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_059</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_060</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_061</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_062</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_063</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_064</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_065</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_066</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_067</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_068</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_069</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_070</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_071</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_072</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_073</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_074</t>
+  </si>
+  <si>
+    <t>TC_WEB_FUNC_075</t>
+  </si>
+  <si>
     <t>TC_WEB_SYS_001</t>
   </si>
   <si>
@@ -1241,6 +1844,189 @@
     <t>Console logging filter active in production compile.</t>
   </si>
   <si>
+    <t>TC_WEB_SYS_023</t>
+  </si>
+  <si>
+    <t>Verify Profile Page behaves correctly under Boundary Checks conditions (expanded case 023).</t>
+  </si>
+  <si>
+    <t>Verified Profile Page execution under Boundary Checks conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_024</t>
+  </si>
+  <si>
+    <t>Verify Alerts &amp; Toasts behaves correctly under Error Recovery conditions (expanded case 024).</t>
+  </si>
+  <si>
+    <t>Verified Alerts &amp; Toasts execution under Error Recovery conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_025</t>
+  </si>
+  <si>
+    <t>Verify Forms behaves correctly under Mobile Views conditions (expanded case 025).</t>
+  </si>
+  <si>
+    <t>Verified Forms execution under Mobile Views conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_026</t>
+  </si>
+  <si>
+    <t>Verify Buttons behaves correctly under Desktop Sizing conditions (expanded case 026).</t>
+  </si>
+  <si>
+    <t>Verified Buttons execution under Desktop Sizing conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_027</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_028</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_029</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_030</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_031</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_032</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_033</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_034</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_035</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_036</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_037</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_038</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_039</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_040</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_041</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_042</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_043</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_044</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_045</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_046</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_047</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_048</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_049</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_050</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_051</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_052</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_053</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_054</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_055</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_056</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_057</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_058</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_059</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_060</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_061</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_062</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_063</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_064</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_065</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_066</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_067</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_068</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_069</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_070</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_071</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_072</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_073</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_074</t>
+  </si>
+  <si>
+    <t>TC_WEB_SYS_075</t>
+  </si>
+  <si>
     <t>TC_WEB_VAL_001</t>
   </si>
   <si>
@@ -1518,6 +2304,183 @@
   </si>
   <si>
     <t>Verified frame-ancestors block active on website responses.</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_021</t>
+  </si>
+  <si>
+    <t>Verify Itinerary Result behaves correctly under Touch Target Limits conditions (expanded case 021).</t>
+  </si>
+  <si>
+    <t>Verified Itinerary Result execution under Touch Target Limits conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_022</t>
+  </si>
+  <si>
+    <t>Verify Settings Page behaves correctly under State Storage Sync conditions (expanded case 022).</t>
+  </si>
+  <si>
+    <t>Verified Settings Page execution under State Storage Sync conditions successfully.</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_023</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_024</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_025</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_026</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_027</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_028</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_029</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_030</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_031</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_032</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_033</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_034</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_035</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_036</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_037</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_038</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_039</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_040</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_041</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_042</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_043</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_044</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_045</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_046</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_047</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_048</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_049</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_050</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_051</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_052</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_053</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_054</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_055</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_056</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_057</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_058</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_059</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_060</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_061</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_062</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_063</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_064</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_065</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_066</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_067</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_068</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_069</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_070</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_071</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_072</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_073</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_074</t>
+  </si>
+  <si>
+    <t>TC_WEB_VAL_075</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +3045,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="5">
-        <v>104</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -2090,7 +3053,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="5">
-        <v>104</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -2147,10 +3110,10 @@
         <v>23</v>
       </c>
       <c r="C21" s="10">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D21" s="10">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="E21" s="10">
         <v>0</v>
@@ -2167,10 +3130,10 @@
         <v>24</v>
       </c>
       <c r="C22" s="10">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D22" s="10">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E22" s="10">
         <v>0</v>
@@ -2187,10 +3150,10 @@
         <v>25</v>
       </c>
       <c r="C23" s="10">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D23" s="10">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E23" s="10">
         <v>0</v>
@@ -2207,10 +3170,10 @@
         <v>26</v>
       </c>
       <c r="C24" s="10">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="D24" s="10">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E24" s="10">
         <v>0</v>
@@ -2230,7 +3193,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2940,19 +3903,19 @@
         <v>155</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="F28" s="15" t="s">
         <v>158</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>159</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>39</v>
@@ -2963,22 +3926,22 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D29" s="20" t="s">
+      <c r="E29" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="F29" s="20" t="s">
         <v>162</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>163</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>39</v>
@@ -2989,22 +3952,22 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="F30" s="15" t="s">
         <v>166</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>167</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>39</v>
@@ -3015,22 +3978,22 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D31" s="20" t="s">
+      <c r="E31" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="F31" s="20" t="s">
         <v>170</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>171</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>39</v>
@@ -3041,22 +4004,22 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="15" t="s">
+      <c r="E32" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="F32" s="15" t="s">
         <v>174</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>175</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>39</v>
@@ -3067,22 +4030,22 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" s="20" t="s">
+      <c r="E33" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="F33" s="20" t="s">
         <v>178</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>179</v>
       </c>
       <c r="G33" s="16" t="s">
         <v>39</v>
@@ -3093,22 +4056,22 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="14" t="s">
+      <c r="E34" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="F34" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>39</v>
@@ -3119,22 +4082,22 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="D35" s="20" t="s">
+      <c r="F35" s="20" t="s">
         <v>186</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>187</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>39</v>
@@ -3145,19 +4108,19 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="B36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="E36" s="15" t="s">
         <v>189</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>183</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>190</v>
@@ -3174,10 +4137,10 @@
         <v>191</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>192</v>
@@ -3200,10 +4163,10 @@
         <v>195</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>196</v>
@@ -3226,19 +4189,19 @@
         <v>199</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>39</v>
@@ -3249,22 +4212,22 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>39</v>
@@ -3275,19 +4238,19 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>204</v>
+        <v>35</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="F41" s="20" t="s">
         <v>211</v>
@@ -3304,19 +4267,19 @@
         <v>212</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>213</v>
       </c>
       <c r="E42" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F42" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>39</v>
@@ -3327,22 +4290,22 @@
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="19" t="s">
+      <c r="E43" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F43" s="20" t="s">
         <v>217</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>220</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>39</v>
@@ -3353,22 +4316,22 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>39</v>
@@ -3379,22 +4342,22 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>39</v>
@@ -3405,22 +4368,22 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>39</v>
@@ -3431,22 +4394,22 @@
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" s="19" t="s">
         <v>108</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>39</v>
@@ -3457,22 +4420,22 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G48" s="16" t="s">
         <v>39</v>
@@ -3483,22 +4446,22 @@
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>39</v>
@@ -3509,22 +4472,22 @@
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>39</v>
@@ -3535,22 +4498,22 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>249</v>
+        <v>197</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>39</v>
@@ -3561,22 +4524,22 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>39</v>
@@ -3587,22 +4550,22 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>39</v>
@@ -3613,22 +4576,22 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>256</v>
+        <v>35</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>262</v>
+        <v>157</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>39</v>
@@ -3639,22 +4602,22 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>256</v>
+        <v>46</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>266</v>
+        <v>161</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>39</v>
@@ -3665,22 +4628,22 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>269</v>
+        <v>55</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>39</v>
@@ -3691,22 +4654,22 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>269</v>
+        <v>73</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>275</v>
+        <v>169</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>39</v>
@@ -3717,22 +4680,22 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>279</v>
+        <v>173</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>39</v>
@@ -3743,22 +4706,22 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>39</v>
@@ -3769,22 +4732,22 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="G60" s="16" t="s">
         <v>39</v>
@@ -3795,22 +4758,22 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>291</v>
+        <v>185</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>39</v>
@@ -3821,22 +4784,22 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>294</v>
+        <v>126</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>296</v>
+        <v>189</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>39</v>
@@ -3847,22 +4810,22 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>299</v>
+        <v>131</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>301</v>
+        <v>193</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>39</v>
@@ -3873,22 +4836,22 @@
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>304</v>
+        <v>136</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>306</v>
+        <v>197</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>39</v>
@@ -3899,22 +4862,22 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>304</v>
+        <v>200</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>310</v>
+        <v>202</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="G65" s="16" t="s">
         <v>39</v>
@@ -3925,22 +4888,22 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>313</v>
+        <v>205</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>315</v>
+        <v>207</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>39</v>
@@ -3951,22 +4914,22 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>319</v>
+        <v>157</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="G67" s="16" t="s">
         <v>39</v>
@@ -3977,22 +4940,22 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>322</v>
+        <v>46</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="G68" s="16" t="s">
         <v>39</v>
@@ -4003,22 +4966,22 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>322</v>
+        <v>55</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="G69" s="16" t="s">
         <v>39</v>
@@ -4029,22 +4992,22 @@
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>322</v>
+        <v>73</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>332</v>
+        <v>169</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="G70" s="16" t="s">
         <v>39</v>
@@ -4055,22 +5018,22 @@
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>337</v>
+        <v>173</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="G71" s="16" t="s">
         <v>39</v>
@@ -4081,22 +5044,22 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>340</v>
+        <v>103</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>342</v>
+        <v>177</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>39</v>
@@ -4107,22 +5070,22 @@
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>345</v>
+        <v>108</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>346</v>
+        <v>306</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>347</v>
+        <v>181</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>39</v>
@@ -4133,22 +5096,22 @@
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>350</v>
+        <v>117</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="G74" s="16" t="s">
         <v>39</v>
@@ -4159,22 +5122,22 @@
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>355</v>
+        <v>126</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>357</v>
+        <v>189</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>39</v>
@@ -4185,22 +5148,22 @@
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>359</v>
+        <v>314</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>362</v>
+        <v>193</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>363</v>
+        <v>316</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>39</v>
@@ -4211,22 +5174,22 @@
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>364</v>
+        <v>317</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>365</v>
+        <v>318</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>366</v>
+        <v>319</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>39</v>
@@ -4237,22 +5200,22 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>369</v>
+        <v>322</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>370</v>
+        <v>318</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>39</v>
@@ -4263,22 +5226,22 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>375</v>
+        <v>318</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>39</v>
@@ -4289,22 +5252,22 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>380</v>
+        <v>318</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>382</v>
+        <v>332</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>39</v>
@@ -4315,22 +5278,22 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>387</v>
+        <v>336</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>39</v>
@@ -4341,22 +5304,22 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>390</v>
+        <v>318</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>392</v>
+        <v>340</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>393</v>
+        <v>341</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>39</v>
@@ -4367,22 +5330,22 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>394</v>
+        <v>342</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>395</v>
+        <v>343</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="G83" s="16" t="s">
         <v>39</v>
@@ -4393,22 +5356,22 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>399</v>
+        <v>347</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>400</v>
+        <v>343</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>401</v>
+        <v>348</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>402</v>
+        <v>345</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>39</v>
@@ -4419,22 +5382,22 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>404</v>
+        <v>350</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>406</v>
+        <v>351</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>407</v>
+        <v>345</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>408</v>
+        <v>352</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>39</v>
@@ -4445,22 +5408,22 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>410</v>
+        <v>343</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>411</v>
+        <v>354</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>412</v>
+        <v>355</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>413</v>
+        <v>356</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>39</v>
@@ -4471,22 +5434,22 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>414</v>
+        <v>357</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>410</v>
+        <v>86</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>415</v>
+        <v>358</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>416</v>
+        <v>359</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>417</v>
+        <v>360</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>39</v>
@@ -4497,22 +5460,22 @@
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>418</v>
+        <v>361</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>410</v>
+        <v>86</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>419</v>
+        <v>362</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>420</v>
+        <v>363</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>39</v>
@@ -4523,22 +5486,22 @@
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>422</v>
+        <v>365</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>424</v>
+        <v>368</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>39</v>
@@ -4549,22 +5512,22 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>426</v>
+        <v>370</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>427</v>
+        <v>366</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>428</v>
+        <v>371</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>429</v>
+        <v>372</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>430</v>
+        <v>373</v>
       </c>
       <c r="G90" s="16" t="s">
         <v>39</v>
@@ -4575,22 +5538,22 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>432</v>
+        <v>103</v>
       </c>
       <c r="D91" s="20" t="s">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>434</v>
+        <v>376</v>
       </c>
       <c r="F91" s="20" t="s">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>39</v>
@@ -4601,22 +5564,22 @@
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>436</v>
+        <v>378</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>437</v>
+        <v>379</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>438</v>
+        <v>380</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="G92" s="16" t="s">
         <v>39</v>
@@ -4627,22 +5590,22 @@
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="D93" s="20" t="s">
-        <v>443</v>
+        <v>385</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>444</v>
+        <v>386</v>
       </c>
       <c r="F93" s="20" t="s">
-        <v>445</v>
+        <v>387</v>
       </c>
       <c r="G93" s="16" t="s">
         <v>39</v>
@@ -4653,22 +5616,22 @@
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>446</v>
+        <v>388</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>442</v>
+        <v>103</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>448</v>
+        <v>390</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>449</v>
+        <v>391</v>
       </c>
       <c r="G94" s="16" t="s">
         <v>39</v>
@@ -4679,22 +5642,22 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>450</v>
+        <v>392</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>451</v>
+        <v>108</v>
       </c>
       <c r="D95" s="20" t="s">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>453</v>
+        <v>394</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>454</v>
+        <v>395</v>
       </c>
       <c r="G95" s="16" t="s">
         <v>39</v>
@@ -4705,22 +5668,22 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>455</v>
+        <v>396</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>458</v>
+        <v>398</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>459</v>
+        <v>399</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>39</v>
@@ -4731,22 +5694,22 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="D97" s="20" t="s">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>462</v>
+        <v>398</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>463</v>
+        <v>402</v>
       </c>
       <c r="G97" s="16" t="s">
         <v>39</v>
@@ -4757,22 +5720,22 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>464</v>
+        <v>403</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>466</v>
+        <v>398</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>39</v>
@@ -4783,22 +5746,22 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>468</v>
+        <v>406</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>469</v>
+        <v>108</v>
       </c>
       <c r="D99" s="20" t="s">
-        <v>470</v>
+        <v>407</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>471</v>
+        <v>398</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>472</v>
+        <v>408</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>39</v>
@@ -4809,22 +5772,22 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>473</v>
+        <v>409</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>474</v>
+        <v>108</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>475</v>
+        <v>410</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>476</v>
+        <v>411</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>477</v>
+        <v>412</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>39</v>
@@ -4835,22 +5798,22 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>478</v>
+        <v>413</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>479</v>
+        <v>108</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="G101" s="16" t="s">
         <v>39</v>
@@ -4861,22 +5824,22 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>483</v>
+        <v>417</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>479</v>
+        <v>418</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>484</v>
+        <v>419</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>485</v>
+        <v>420</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>486</v>
+        <v>421</v>
       </c>
       <c r="G102" s="16" t="s">
         <v>39</v>
@@ -4887,22 +5850,22 @@
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>487</v>
+        <v>422</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>488</v>
+        <v>418</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>490</v>
+        <v>424</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>39</v>
@@ -4913,22 +5876,22 @@
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>494</v>
+        <v>427</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>496</v>
+        <v>429</v>
       </c>
       <c r="G104" s="16" t="s">
         <v>39</v>
@@ -4939,27 +5902,5123 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="F107" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H107" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D109" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F109" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H109" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="F111" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H111" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F113" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="G113" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G114" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F115" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G115" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F116" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G116" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="G117" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F118" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G118" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H118" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F119" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G119" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H119" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E120" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="G120" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H120" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="B121" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F121" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H121" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E122" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F122" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H122" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="B123" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F123" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="G123" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H123" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E124" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G124" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F125" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G125" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F126" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="G126" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H126" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="B127" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D127" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F127" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="G127" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H127" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E128" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F128" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="G128" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H128" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="B129" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D129" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E129" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F129" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="G129" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H129" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="E130" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F130" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G130" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D131" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="E131" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F131" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="G131" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H131" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E132" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F132" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="G132" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D133" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E133" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F133" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G133" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H133" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E134" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F134" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="G134" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H134" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D135" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="E135" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F135" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="G135" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H135" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="E136" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F136" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G136" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H136" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B137" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D137" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F137" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="G137" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E138" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F138" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="G138" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H138" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D139" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F139" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G139" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H139" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="E140" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F140" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="G140" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H140" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D141" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="G141" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H141" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E142" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F142" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="G142" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H142" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="G143" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H143" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="E144" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F144" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="G144" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H144" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="17" t="s">
         <v>497</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B145" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D145" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F145" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G145" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H145" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="E146" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F146" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="G146" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H146" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="147" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D147" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F147" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="G147" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H147" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="E148" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F148" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="G148" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D149" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F149" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="G149" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H149" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D150" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E150" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F150" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="G150" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H150" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D151" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="E151" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F151" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="G151" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H151" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="D152" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="E152" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="F152" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="G152" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="D153" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="F153" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="G153" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H153" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="E154" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="F154" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="G154" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H154" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="D155" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="F155" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="G155" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H155" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E156" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="F156" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="G156" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H156" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="B157" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="D157" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="G157" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H157" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="E158" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="F158" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="G158" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H158" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="159" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="D159" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="F159" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="G159" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H159" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="B160" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C160" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="D160" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="E160" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="F160" s="15" t="s">
+        <v>544</v>
+      </c>
+      <c r="G160" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H160" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="161" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="B161" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="D161" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="E161" s="20" t="s">
+        <v>548</v>
+      </c>
+      <c r="F161" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="G161" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H161" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C162" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="D162" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="E162" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="F162" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="G162" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H162" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="B163" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="D163" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="E163" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="F163" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="G163" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H163" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C164" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="E164" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="F164" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="G164" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H164" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="165" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="B165" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C165" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="D165" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="F165" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="G165" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H165" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B166" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C166" s="14" t="s">
+        <v>571</v>
+      </c>
+      <c r="D166" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="E166" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="F166" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="G166" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H166" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="167" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="17" t="s">
+        <v>575</v>
+      </c>
+      <c r="B167" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C167" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="D167" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="F167" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="G167" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H167" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C168" s="14" t="s">
+        <v>581</v>
+      </c>
+      <c r="D168" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="E168" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="F168" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="G168" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H168" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B169" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C169" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="D169" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="F169" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="G169" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H169" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="170" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C170" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="D170" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="E170" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="F170" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="G170" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H170" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="B171" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C171" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="D171" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="F171" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="G171" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H171" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="D172" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="E172" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="F172" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="G172" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H172" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="B173" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C173" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="D173" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="F173" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="G173" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H173" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="B174" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C174" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D174" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="E174" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F174" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="G174" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H174" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="175" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="17" t="s">
+        <v>613</v>
+      </c>
+      <c r="B175" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D175" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="E175" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F175" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="G175" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H175" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B176" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D176" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="E176" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F176" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="G176" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H176" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="177" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="B177" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C177" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D177" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="E177" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F177" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="G177" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H177" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="178" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C178" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D178" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E178" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F178" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G178" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H178" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="179" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="B179" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C179" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D179" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E179" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F179" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G179" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H179" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D180" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F180" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="G180" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H180" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C181" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D181" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E181" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F181" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G181" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H181" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E182" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F182" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G182" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H182" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="B183" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C183" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D183" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="E183" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F183" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="G183" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H183" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C184" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D184" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E184" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F184" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="G184" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H184" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C185" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D185" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E185" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F185" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="G185" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H185" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C186" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D186" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E186" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F186" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="G186" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H186" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C187" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D187" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="E187" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F187" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G187" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H187" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C188" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E188" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F188" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="G188" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H188" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="17" t="s">
+        <v>633</v>
+      </c>
+      <c r="B189" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C189" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D189" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="E189" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F189" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G189" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H189" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C190" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D190" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E190" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F190" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="G190" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H190" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B191" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C191" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D191" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E191" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="G191" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H191" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="B192" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C192" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D192" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="E192" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F192" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G192" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H192" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="B193" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C193" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D193" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="E193" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F193" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="G193" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H193" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C194" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D194" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="E194" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F194" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="G194" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H194" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="B195" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C195" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D195" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="E195" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F195" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="G195" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H195" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C196" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D196" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E196" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F196" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G196" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H196" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="B197" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C197" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D197" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="E197" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F197" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="G197" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H197" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D198" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E198" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F198" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="G198" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H198" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="17" t="s">
+        <v>643</v>
+      </c>
+      <c r="B199" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C199" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D199" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="E199" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F199" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="G199" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H199" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C200" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D200" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E200" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F200" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="G200" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H200" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="17" t="s">
+        <v>645</v>
+      </c>
+      <c r="B201" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C201" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D201" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E201" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F201" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="G201" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H201" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="B202" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C202" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D202" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E202" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F202" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="G202" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H202" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="17" t="s">
+        <v>647</v>
+      </c>
+      <c r="B203" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C203" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D203" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E203" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F203" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="G203" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H203" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C204" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D204" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E204" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F204" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G204" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H204" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="205" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="B205" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C205" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D205" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E205" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F205" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="G205" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H205" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="206" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="B206" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C206" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D206" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E206" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F206" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="G206" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H206" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="B207" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C207" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D207" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E207" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F207" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="G207" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H207" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="B208" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C208" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D208" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E208" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F208" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G208" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H208" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="209" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="17" t="s">
+        <v>653</v>
+      </c>
+      <c r="B209" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C209" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D209" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="E209" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F209" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="G209" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H209" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="B210" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C210" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D210" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E210" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F210" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="G210" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H210" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="211" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="B211" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C211" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D211" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="E211" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F211" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="G211" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H211" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="212" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C212" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D212" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="E212" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F212" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="G212" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H212" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="213" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="B213" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C213" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D213" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="E213" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F213" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G213" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H213" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="214" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="12" t="s">
+        <v>658</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C214" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D214" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E214" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F214" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="G214" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H214" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="215" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="B215" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C215" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D215" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E215" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F215" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="G215" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H215" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="216" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C216" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D216" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E216" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F216" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G216" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H216" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="217" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="B217" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C217" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D217" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E217" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F217" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="G217" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H217" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="218" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C218" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D218" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E218" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F218" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="G218" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H218" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="219" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="B219" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C219" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D219" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="E219" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F219" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="G219" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H219" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="220" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="B220" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C220" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D220" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E220" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F220" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="G220" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H220" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="221" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="B221" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C221" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D221" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E221" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F221" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="G221" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H221" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C222" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D222" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E222" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F222" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="G222" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H222" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="223" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="B223" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C223" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D223" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E223" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F223" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="G223" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H223" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="224" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C224" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D224" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="E224" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F224" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="G224" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H224" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="225" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="B225" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C225" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D225" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E225" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F225" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="G225" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H225" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="226" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C226" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D226" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E226" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F226" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="G226" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H226" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="227" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="17" t="s">
+        <v>671</v>
+      </c>
+      <c r="B227" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="D105" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="E105" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="F105" s="20" t="s">
-        <v>501</v>
-      </c>
-      <c r="G105" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H105" s="18" t="s">
+      <c r="C227" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D227" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="E227" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="F227" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="G227" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H227" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C228" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="D228" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="E228" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="F228" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="G228" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H228" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="229" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="B229" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C229" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D229" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="E229" s="20" t="s">
+        <v>682</v>
+      </c>
+      <c r="F229" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="G229" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H229" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="230" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="B230" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C230" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="D230" s="15" t="s">
+        <v>685</v>
+      </c>
+      <c r="E230" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="G230" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H230" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="231" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="B231" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C231" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="D231" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="E231" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="F231" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="G231" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H231" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B232" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C232" s="14" t="s">
+        <v>694</v>
+      </c>
+      <c r="D232" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="E232" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="G232" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H232" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="233" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="B233" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C233" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="D233" s="20" t="s">
+        <v>700</v>
+      </c>
+      <c r="E233" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="F233" s="20" t="s">
+        <v>702</v>
+      </c>
+      <c r="G233" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H233" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="234" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="B234" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C234" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="D234" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="E234" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="F234" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="G234" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H234" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="235" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="B235" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C235" s="19" t="s">
+        <v>704</v>
+      </c>
+      <c r="D235" s="20" t="s">
+        <v>709</v>
+      </c>
+      <c r="E235" s="20" t="s">
+        <v>710</v>
+      </c>
+      <c r="F235" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="G235" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H235" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="B236" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C236" s="14" t="s">
+        <v>713</v>
+      </c>
+      <c r="D236" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="E236" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="F236" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="G236" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H236" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="237" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="B237" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C237" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="D237" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="E237" s="20" t="s">
+        <v>720</v>
+      </c>
+      <c r="F237" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="G237" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H237" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="238" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B238" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C238" s="14" t="s">
+        <v>718</v>
+      </c>
+      <c r="D238" s="15" t="s">
+        <v>723</v>
+      </c>
+      <c r="E238" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="F238" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="G238" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H238" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="B239" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C239" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="D239" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="E239" s="20" t="s">
+        <v>728</v>
+      </c>
+      <c r="F239" s="20" t="s">
+        <v>729</v>
+      </c>
+      <c r="G239" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H239" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="240" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="B240" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C240" s="14" t="s">
+        <v>731</v>
+      </c>
+      <c r="D240" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E240" s="15" t="s">
+        <v>733</v>
+      </c>
+      <c r="F240" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="G240" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H240" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="241" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="B241" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C241" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="D241" s="20" t="s">
+        <v>737</v>
+      </c>
+      <c r="E241" s="20" t="s">
+        <v>738</v>
+      </c>
+      <c r="F241" s="20" t="s">
+        <v>739</v>
+      </c>
+      <c r="G241" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H241" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="242" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B242" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C242" s="14" t="s">
+        <v>741</v>
+      </c>
+      <c r="D242" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="E242" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="F242" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="G242" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H242" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="B243" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C243" s="19" t="s">
+        <v>741</v>
+      </c>
+      <c r="D243" s="20" t="s">
+        <v>746</v>
+      </c>
+      <c r="E243" s="20" t="s">
+        <v>747</v>
+      </c>
+      <c r="F243" s="20" t="s">
+        <v>748</v>
+      </c>
+      <c r="G243" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H243" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="244" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B244" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C244" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="D244" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="E244" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="F244" s="15" t="s">
+        <v>753</v>
+      </c>
+      <c r="G244" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H244" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="245" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="B245" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C245" s="19" t="s">
+        <v>755</v>
+      </c>
+      <c r="D245" s="20" t="s">
+        <v>756</v>
+      </c>
+      <c r="E245" s="20" t="s">
+        <v>757</v>
+      </c>
+      <c r="F245" s="20" t="s">
+        <v>758</v>
+      </c>
+      <c r="G245" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H245" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="246" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B246" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C246" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="D246" s="15" t="s">
+        <v>761</v>
+      </c>
+      <c r="E246" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="F246" s="15" t="s">
+        <v>763</v>
+      </c>
+      <c r="G246" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H246" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="247" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="B247" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C247" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D247" s="20" t="s">
+        <v>765</v>
+      </c>
+      <c r="E247" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F247" s="20" t="s">
+        <v>766</v>
+      </c>
+      <c r="G247" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H247" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="B248" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C248" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D248" s="15" t="s">
+        <v>768</v>
+      </c>
+      <c r="E248" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F248" s="15" t="s">
+        <v>769</v>
+      </c>
+      <c r="G248" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H248" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="B249" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C249" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D249" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="E249" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F249" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="G249" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H249" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="12" t="s">
+        <v>771</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C250" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D250" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="E250" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F250" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="G250" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H250" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="B251" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C251" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D251" s="20" t="s">
+        <v>617</v>
+      </c>
+      <c r="E251" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F251" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="G251" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H251" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C252" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D252" s="15" t="s">
+        <v>620</v>
+      </c>
+      <c r="E252" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F252" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="G252" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H252" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" s="17" t="s">
+        <v>774</v>
+      </c>
+      <c r="B253" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C253" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D253" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E253" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F253" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G253" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H253" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="254" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="B254" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C254" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D254" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E254" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F254" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="G254" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H254" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="B255" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C255" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D255" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="E255" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F255" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G255" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H255" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="256" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="B256" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C256" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D256" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E256" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F256" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="G256" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H256" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="17" t="s">
+        <v>778</v>
+      </c>
+      <c r="B257" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C257" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D257" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E257" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F257" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G257" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H257" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="258" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="12" t="s">
+        <v>779</v>
+      </c>
+      <c r="B258" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C258" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D258" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="E258" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F258" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G258" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H258" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="259" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="B259" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C259" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D259" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="E259" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F259" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="G259" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H259" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="260" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="B260" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C260" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D260" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E260" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F260" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="G260" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H260" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="261" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" s="17" t="s">
+        <v>782</v>
+      </c>
+      <c r="B261" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C261" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D261" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E261" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F261" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G261" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H261" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="262" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C262" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D262" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E262" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F262" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="G262" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H262" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="263" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="B263" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C263" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D263" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E263" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F263" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="G263" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H263" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="264" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C264" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D264" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E264" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F264" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G264" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H264" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="B265" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C265" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D265" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="E265" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F265" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G265" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H265" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C266" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D266" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="E266" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F266" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G266" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H266" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="B267" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C267" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D267" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E267" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F267" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="G267" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H267" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="268" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C268" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D268" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E268" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F268" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G268" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H268" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="B269" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C269" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D269" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E269" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F269" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="G269" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H269" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C270" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D270" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E270" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F270" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="G270" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H270" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="B271" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C271" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D271" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E271" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F271" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="G271" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H271" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="272" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C272" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D272" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E272" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F272" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="G272" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H272" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="273" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="B273" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C273" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D273" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="E273" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F273" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="G273" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H273" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="274" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C274" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D274" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E274" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F274" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G274" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H274" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="275" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="B275" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C275" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D275" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E275" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F275" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G275" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H275" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="276" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C276" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D276" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="E276" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="F276" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="G276" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H276" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="277" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="B277" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C277" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D277" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E277" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F277" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="G277" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H277" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="278" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B278" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C278" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D278" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E278" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F278" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="G278" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H278" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="279" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="17" t="s">
+        <v>800</v>
+      </c>
+      <c r="B279" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C279" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D279" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E279" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F279" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="G279" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H279" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="280" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="B280" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C280" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D280" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="E280" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F280" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G280" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H280" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="B281" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C281" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D281" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="E281" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F281" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="G281" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H281" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="282" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="B282" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C282" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D282" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E282" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F282" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="G282" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H282" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="283" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="B283" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C283" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D283" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E283" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F283" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G283" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H283" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="284" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="B284" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C284" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D284" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E284" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F284" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="G284" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H284" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="285" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="B285" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C285" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D285" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="E285" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F285" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="G285" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H285" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="286" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="B286" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C286" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D286" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="E286" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F286" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="G286" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H286" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" s="17" t="s">
+        <v>808</v>
+      </c>
+      <c r="B287" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C287" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D287" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="E287" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F287" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="G287" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H287" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C288" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D288" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E288" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F288" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="G288" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H288" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="B289" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C289" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D289" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="E289" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F289" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="G289" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H289" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="B290" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C290" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D290" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="E290" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F290" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="G290" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H290" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="B291" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C291" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D291" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E291" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="F291" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="G291" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H291" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C292" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D292" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E292" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F292" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="G292" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H292" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" s="17" t="s">
+        <v>814</v>
+      </c>
+      <c r="B293" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C293" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D293" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E293" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F293" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="G293" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H293" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="B294" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C294" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D294" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="E294" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F294" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="G294" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H294" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="B295" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C295" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D295" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E295" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F295" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G295" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H295" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C296" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D296" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="E296" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F296" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="G296" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H296" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="B297" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C297" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D297" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="E297" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F297" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="G297" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H297" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C298" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D298" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="E298" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F298" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="G298" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H298" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="B299" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C299" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D299" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="E299" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F299" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="G299" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H299" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C300" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D300" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E300" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F300" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="G300" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H300" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="B301" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C301" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D301" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="E301" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F301" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="G301" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H301" s="18" t="s">
         <v>40</v>
       </c>
     </row>
